--- a/input/Template_EMIS_Access.xlsx
+++ b/input/Template_EMIS_Access.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted-my.sharepoint.com/personal/martina_vit_impact-initiatives_org/Documents/PiN_app_dev/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765B3A74-2B1B-404D-908F-38838E10F202}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA71EC7E-9CA2-4611-B014-4DFA36F97091}"/>
   <bookViews>
-    <workbookView xWindow="-19290" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator" sheetId="3" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Admin Pcode</t>
   </si>
@@ -79,21 +79,6 @@
   </si>
   <si>
     <t>Enrolled students -- Children/Enfants (5-17)</t>
-  </si>
-  <si>
-    <t>Enrolled Girls/Filles (5-17)</t>
-  </si>
-  <si>
-    <t>Enrolled Boys/Garcons (5-17)</t>
-  </si>
-  <si>
-    <t>Primary school -- Enrolled students</t>
-  </si>
-  <si>
-    <t>Intermediate school or secondary school  -- Enrolled students</t>
-  </si>
-  <si>
-    <t>Secondary school -- Enrolled students</t>
   </si>
 </sst>
 </file>
@@ -191,16 +176,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -550,43 +529,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30F2C5B-1A85-47E0-8D30-CF37F49EBEDE}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="6" customWidth="1"/>
-    <col min="4" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="8" width="22.85546875" style="3" customWidth="1"/>
+    <col min="1" max="2" width="14.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
   </sheetData>
   <protectedRanges>
